--- a/data/trans_bre/P32-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 1,12</t>
+          <t>-5,95; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -3,74</t>
+          <t>-12,43; -3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,92</t>
+          <t>-5,55; 4,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 8,25</t>
+          <t>-9,87; 8,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,08; 50,25</t>
+          <t>-85,42; 59,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,86; -38,07</t>
+          <t>-91,49; -37,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 95,84</t>
+          <t>-55,74; 97,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-96,24; 1298,56</t>
+          <t>-91,91; 3588,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,08</t>
+          <t>-3,55; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,6</t>
+          <t>-7,51; 0,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 0,6</t>
+          <t>-7,01; 0,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 2,14</t>
+          <t>-8,61; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 80,22</t>
+          <t>-100,0; 122,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 18,64</t>
+          <t>-80,52; 8,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 15,61</t>
+          <t>-75,59; 16,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,01; 83,99</t>
+          <t>-87,67; 105,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,84</t>
+          <t>-1,72; 1,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,93</t>
+          <t>-4,5; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -0,07</t>
+          <t>-4,39; -0,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -0,4</t>
+          <t>-7,8; -0,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 56,75</t>
+          <t>-74,96; 67,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,67</t>
+          <t>-91,58; 17,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-88,72; 3,04</t>
+          <t>-89,59; 1,03</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,32</t>
+          <t>-1,56; 3,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,7; -4,83</t>
+          <t>-10,84; -5,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 0,41</t>
+          <t>-7,14; -0,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,19</t>
+          <t>-5,34; 0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-78,72; 19,84</t>
+          <t>-81,74; 8,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 30,82</t>
+          <t>-84,37; 29,71</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,61</t>
+          <t>-8,06; 1,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 0,19</t>
+          <t>-6,33; 0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 2,65</t>
+          <t>-6,67; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -1,97</t>
+          <t>-9,83; -1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,58</t>
+          <t>-100,0; 162,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,48</t>
+          <t>-100,0; 261,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-87,88; 94,88</t>
+          <t>-91,42; 88,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,08; -23,6</t>
+          <t>-84,02; -21,59</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 0,0</t>
+          <t>-6,64; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -2,7</t>
+          <t>-12,11; -2,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,07</t>
+          <t>-1,83; 6,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -3,26</t>
+          <t>-9,75; -3,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -62,0</t>
+          <t>-100,0; -61,52</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,0</t>
+          <t>-6,77; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 0,0</t>
+          <t>-12,66; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 0,0</t>
+          <t>-8,74; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,65</t>
+          <t>-1,96; 5,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,07</t>
+          <t>-2,35; -0,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -2,87</t>
+          <t>-6,12; -3,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,61</t>
+          <t>-3,37; -0,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,92</t>
+          <t>-5,85; -2,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 2,35</t>
+          <t>-73,81; -4,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,37; -46,23</t>
+          <t>-81,63; -51,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,58; -10,58</t>
+          <t>-57,76; -9,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-81,51; -35,92</t>
+          <t>-81,43; -38,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-12,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,36</t>
+          <t>-5,82; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -3,55</t>
+          <t>-12,19; -3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 4,64</t>
+          <t>-6,02; 5,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 8,7</t>
+          <t>-9,85; 9,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-85,42; 59,86</t>
+          <t>-85,01; 61,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-91,49; -37,33</t>
+          <t>-90,86; -38,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 97,59</t>
+          <t>-59,36; 102,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,91; 3588,3</t>
+          <t>-81,16; 349,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-3,81</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-47,81%</t>
+          <t>-52,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,39</t>
+          <t>-3,6; 1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 0,36</t>
+          <t>-7,35; 0,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 0,54</t>
+          <t>-6,69; 0,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,0</t>
+          <t>-9,36; 1,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,46</t>
+          <t>-100,0; 123,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 8,42</t>
+          <t>-77,91; 9,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 16,18</t>
+          <t>-74,71; 8,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,67; 105,57</t>
+          <t>-90,7; 46,16</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-64,36%</t>
+          <t>-69,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,97</t>
+          <t>-1,64; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,92</t>
+          <t>-4,52; 1,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,21</t>
+          <t>-4,23; -0,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,74</t>
+          <t>-8,81; -1,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 444,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,96; 67,77</t>
+          <t>-74,51; 64,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-91,58; 17,35</t>
+          <t>-91,4; 35,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,59; 1,03</t>
+          <t>-91,63; -21,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-57,04%</t>
+          <t>-49,78%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,43</t>
+          <t>-1,69; 3,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -5,11</t>
+          <t>-10,8; -5,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -0,17</t>
+          <t>-6,49; 0,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,32</t>
+          <t>-5,18; 0,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 8,47</t>
+          <t>-79,8; 17,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,37; 29,71</t>
+          <t>-83,17; 34,82</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-62,67%</t>
+          <t>-61,23%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,01</t>
+          <t>-8,32; 0,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,48</t>
+          <t>-6,24; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,42</t>
+          <t>-6,82; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -1,79</t>
+          <t>-9,76; -1,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 162,31</t>
+          <t>-100,0; 97,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 261,54</t>
+          <t>-100,0; 119,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-91,42; 88,94</t>
+          <t>-100,0; 84,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-84,02; -21,59</t>
+          <t>-83,57; -15,43</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,73</t>
+          <t>-4,25</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-93,17%</t>
+          <t>-66,6%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,0</t>
+          <t>-6,67; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -2,61</t>
+          <t>-12,97; -3,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,5</t>
+          <t>-1,82; 6,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -3,28</t>
+          <t>-8,02; -0,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -61,52</t>
+          <t>-91,83; 9,05</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>191,77%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,0</t>
+          <t>-6,89; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 0,0</t>
+          <t>-12,78; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,0</t>
+          <t>-8,51; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,98</t>
+          <t>-1,11; 10,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-61,46%</t>
+          <t>-46,92%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,16</t>
+          <t>-2,36; -0,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -3,12</t>
+          <t>-6,2; -3,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,4</t>
+          <t>-3,52; -0,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -2,04</t>
+          <t>-4,72; -1,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,81; -4,48</t>
+          <t>-71,69; 0,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,63; -51,27</t>
+          <t>-81,97; -50,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,76; -9,03</t>
+          <t>-57,61; -8,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-81,43; -38,19</t>
+          <t>-64,6; -15,54</t>
         </is>
       </c>
     </row>
